--- a/questionnaire_templates/049_custom_suit_design_inquiry--questionnaire_templates.xlsx
+++ b/questionnaire_templates/049_custom_suit_design_inquiry--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'color',_'label':_'what_color_would_you_prefer?',_'value':_'black'}</t>
+          <t>what_color_would_you_prefer?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'color', 'label': 'What color would you prefer?', 'value': 'Black'}</t>
+          <t>What color would you prefer?</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'color',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'color', 'label': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'color',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'color', 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'slim_fit',_'label':_'slim_fit'}</t>
+          <t>slim_fit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'slim_fit', 'label': 'Slim Fit'}</t>
+          <t>Slim Fit</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'regular_fit',_'label':_'regular_fit'}</t>
+          <t>regular_fit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'regular_fit', 'label': 'Regular Fit'}</t>
+          <t>Regular Fit</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_'athletic_fit',_'label':_'athletic_fit'}</t>
+          <t>athletic_fit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': 'athletic_fit', 'label': 'Athletic Fit'}</t>
+          <t>Athletic Fit</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_100,_'name':_'short_jacket',_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 100, 'name': 'short_jacket', 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_110,_'name':_'long_jacket',_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 110, 'name': 'long_jacket', 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_120,_'name':_'three_quarter_length',_'label':_'three-quarter_length'}</t>
+          <t>three-quarter_length</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 120, 'name': 'three_quarter_length', 'label': 'Three-quarter length'}</t>
+          <t>Three-quarter length</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_140,_'name':_'short_sleeves',_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 140, 'name': 'short_sleeves', 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_150,_'name':_'long_sleeves',_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 150, 'name': 'long_sleeves', 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_160,_'name':_'three_quarter_sleeves',_'label':_'three-quarter_sleeves'}</t>
+          <t>three-quarter_sleeves</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 160, 'name': 'three_quarter_sleeves', 'label': 'Three-quarter sleeves'}</t>
+          <t>Three-quarter sleeves</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_180,_'name':_'short_pants',_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 180, 'name': 'short_pants', 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_190,_'name':_'long_pants',_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 190, 'name': 'long_pants', 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_200,_'name':_'three_quarter_pants',_'label':_'three-quarter_pants'}</t>
+          <t>three-quarter_pants</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 200, 'name': 'three_quarter_pants', 'label': 'Three-quarter pants'}</t>
+          <t>Three-quarter pants</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_220,_'name':_'formal_pants',_'label':_'formal'}</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 220, 'name': 'formal_pants', 'label': 'Formal'}</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_230,_'name':_'casual_pants',_'label':_'casual'}</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 230, 'name': 'casual_pants', 'label': 'Casual'}</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_240,_'name':_'athletic_pants',_'label':_'athletic'}</t>
+          <t>athletic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 240, 'name': 'athletic_pants', 'label': 'Athletic'}</t>
+          <t>Athletic</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_260,_'name':_'cotton',_'label':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 260, 'name': 'cotton', 'label': 'Cotton'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_270,_'name':_'wool',_'label':_'wool'}</t>
+          <t>wool</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 270, 'name': 'wool', 'label': 'Wool'}</t>
+          <t>Wool</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_280,_'name':_'linen',_'label':_'linen'}</t>
+          <t>linen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 280, 'name': 'linen', 'label': 'Linen'}</t>
+          <t>Linen</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_300,_'name':_'black',_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 300, 'name': 'black', 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_310,_'name':_'gray',_'label':_'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 310, 'name': 'gray', 'label': 'Gray'}</t>
+          <t>Gray</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_320,_'name':_'beige',_'label':_'beige'}</t>
+          <t>beige</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 320, 'name': 'beige', 'label': 'Beige'}</t>
+          <t>Beige</t>
         </is>
       </c>
     </row>
